--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.66111653182406</v>
+        <v>10.34493143642141</v>
       </c>
       <c r="D2" t="n">
-        <v>64.27311556097959</v>
+        <v>10.44438127865918</v>
       </c>
       <c r="E2" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F2" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.39228203823781</v>
+        <v>4.451245831213645</v>
       </c>
       <c r="D3" t="n">
-        <v>27.99867635334889</v>
+        <v>4.549784907419195</v>
       </c>
       <c r="E3" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F3" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.33689048866312</v>
+        <v>6.067244704407757</v>
       </c>
       <c r="D4" t="n">
-        <v>37.91599151590656</v>
+        <v>6.161348621334817</v>
       </c>
       <c r="E4" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F4" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.67095810082549</v>
+        <v>7.746530691384143</v>
       </c>
       <c r="D5" t="n">
-        <v>47.42373368370188</v>
+        <v>7.706356723601555</v>
       </c>
       <c r="E5" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F5" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.09431051501774</v>
+        <v>3.102825458690383</v>
       </c>
       <c r="D6" t="n">
-        <v>19.29363926555902</v>
+        <v>3.13521638065334</v>
       </c>
       <c r="E6" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F6" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.39488772068706</v>
+        <v>7.701669254611647</v>
       </c>
       <c r="D7" t="n">
-        <v>47.01328538397195</v>
+        <v>7.639658874895443</v>
       </c>
       <c r="E7" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F7" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.69869778041842</v>
+        <v>5.313538389317993</v>
       </c>
       <c r="D8" t="n">
-        <v>33.1243925526757</v>
+        <v>5.382713789809801</v>
       </c>
       <c r="E8" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F8" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.14958059084481</v>
+        <v>5.711806846012281</v>
       </c>
       <c r="D9" t="n">
-        <v>34.6864607344807</v>
+        <v>5.636549869353114</v>
       </c>
       <c r="E9" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F9" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>41.79332174693652</v>
+        <v>6.791414783877185</v>
       </c>
       <c r="D10" t="n">
-        <v>41.25338528960295</v>
+        <v>6.703675109560479</v>
       </c>
       <c r="E10" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F10" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.77878167031295</v>
+        <v>3.539052021425854</v>
       </c>
       <c r="D11" t="n">
-        <v>21.19410771571186</v>
+        <v>3.444042503803178</v>
       </c>
       <c r="E11" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F11" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>40.04570006332459</v>
+        <v>6.507426260290246</v>
       </c>
       <c r="D12" t="n">
-        <v>40.38768369252965</v>
+        <v>6.562998600036068</v>
       </c>
       <c r="E12" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F12" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.14414885073523</v>
+        <v>5.060924188244474</v>
       </c>
       <c r="D13" t="n">
-        <v>30.62942170683311</v>
+        <v>4.97728102736038</v>
       </c>
       <c r="E13" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F13" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>27.49702451833549</v>
+        <v>4.468266484229518</v>
       </c>
       <c r="D14" t="n">
-        <v>27.13386921510754</v>
+        <v>4.409253747454976</v>
       </c>
       <c r="E14" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F14" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>43.2344486450818</v>
+        <v>7.025597904825792</v>
       </c>
       <c r="D15" t="n">
-        <v>42.62479689632119</v>
+        <v>6.926529495652194</v>
       </c>
       <c r="E15" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F15" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>57.29772610391238</v>
+        <v>9.310880491885762</v>
       </c>
       <c r="D16" t="n">
-        <v>56.69588438765434</v>
+        <v>9.21308121299383</v>
       </c>
       <c r="E16" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F16" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>35.77481648314376</v>
+        <v>5.813407678510861</v>
       </c>
       <c r="D17" t="n">
-        <v>35.96205947200785</v>
+        <v>5.843834664201276</v>
       </c>
       <c r="E17" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F17" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>66.11156875563768</v>
+        <v>10.74312992279112</v>
       </c>
       <c r="D18" t="n">
-        <v>65.50656414823814</v>
+        <v>10.6448166740887</v>
       </c>
       <c r="E18" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F18" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>24.6465220389919</v>
+        <v>4.005059831336183</v>
       </c>
       <c r="D19" t="n">
-        <v>24.9519118524317</v>
+        <v>4.054685676020151</v>
       </c>
       <c r="E19" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F19" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>53.40573551139028</v>
+        <v>8.678432020600921</v>
       </c>
       <c r="D20" t="n">
-        <v>52.80753632484354</v>
+        <v>8.581224652787075</v>
       </c>
       <c r="E20" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F20" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>50.7547250021946</v>
+        <v>8.247642812856624</v>
       </c>
       <c r="D21" t="n">
-        <v>50.19607929251846</v>
+        <v>8.156862885034251</v>
       </c>
       <c r="E21" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F21" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>14.44808785584592</v>
+        <v>2.347814276574962</v>
       </c>
       <c r="D22" t="n">
-        <v>14.79459291680656</v>
+        <v>2.404121348981067</v>
       </c>
       <c r="E22" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F22" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>15.83802038152234</v>
+        <v>2.573678311997381</v>
       </c>
       <c r="D23" t="n">
-        <v>15.72729001847823</v>
+        <v>2.555684628002712</v>
       </c>
       <c r="E23" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F23" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>24.20498837992632</v>
+        <v>3.933310611738027</v>
       </c>
       <c r="D24" t="n">
-        <v>23.8281161410332</v>
+        <v>3.872068872917894</v>
       </c>
       <c r="E24" t="n">
-        <v>14.42341056708729</v>
+        <v>2.343804217151684</v>
       </c>
       <c r="F24" t="n">
-        <v>14.30492133897462</v>
+        <v>2.324549717583376</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
